--- a/logs/Consolidado_09_04_2026.xlsx
+++ b/logs/Consolidado_09_04_2026.xlsx
@@ -698,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
